--- a/data/trans_dic/P19C11_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,59</t>
+          <t>4,27; 8,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,31</t>
+          <t>3,67; 7,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,12</t>
+          <t>4,38; 7,24</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,0</t>
+          <t>3,23; 6,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,46</t>
+          <t>2,14; 5,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,54</t>
+          <t>3,16; 5,68</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,86</t>
+          <t>0,79; 4,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,1</t>
+          <t>4,22; 10,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,53</t>
+          <t>1,23; 5,4</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,34</t>
+          <t>4,31; 7,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,32</t>
+          <t>1,52; 4,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,46</t>
+          <t>3,16; 5,55</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,24</t>
+          <t>1,17; 4,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,33</t>
+          <t>2,79; 5,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,25</t>
+          <t>2,55; 4,37</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,58</t>
+          <t>2,29; 4,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,58</t>
+          <t>1,86; 3,6</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,99</t>
+          <t>3,27; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,46</t>
+          <t>3,02; 4,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,52</t>
+          <t>3,4; 4,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21909; 42818</t>
+          <t>21265; 42032</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16896; 32214</t>
+          <t>16170; 31737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41914; 66920</t>
+          <t>41108; 67983</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14684; 31391</t>
+          <t>14487; 30905</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8354; 20602</t>
+          <t>8094; 19796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25468; 45768</t>
+          <t>26067; 46895</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5530; 32108</t>
+          <t>5206; 31651</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7029; 16670</t>
+          <t>6961; 17286</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12645; 45657</t>
+          <t>10173; 44606</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43262; 73242</t>
+          <t>42992; 72491</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14393; 41426</t>
+          <t>14609; 41864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60564; 106858</t>
+          <t>61834; 108565</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4990; 18617</t>
+          <t>5120; 18086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22960; 43392</t>
+          <t>22678; 44503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31027; 53283</t>
+          <t>31934; 54754</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3008</t>
+          <t>0; 2486</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17050; 34058</t>
+          <t>17012; 34166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17708; 35003</t>
+          <t>18150; 35160</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105172; 163504</t>
+          <t>107076; 164267</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107703; 155973</t>
+          <t>105594; 154244</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>228873; 306490</t>
+          <t>230725; 307701</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C11_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,43</t>
+          <t>4,23; 8,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,2</t>
+          <t>3,52; 7,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,24</t>
+          <t>4,4; 6,96</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,89</t>
+          <t>3,24; 6,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,24</t>
+          <t>2,12; 5,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,68</t>
+          <t>3,0; 5,35</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,79</t>
+          <t>2,51; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,48</t>
+          <t>4,08; 9,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,4</t>
+          <t>3,42; 6,47</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,26</t>
+          <t>4,35; 7,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,37</t>
+          <t>3,03; 5,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,55</t>
+          <t>4,12; 6,13</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,12</t>
+          <t>1,61; 4,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,47</t>
+          <t>3,4; 5,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,37</t>
+          <t>3,06; 4,83</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,59</t>
+          <t>2,19; 4,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,6</t>
+          <t>1,73; 3,54</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,01</t>
+          <t>3,98; 5,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,41</t>
+          <t>3,67; 4,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,54</t>
+          <t>3,93; 4,83</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>56855</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21265; 42032</t>
+          <t>22910; 44194</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16170; 31737</t>
+          <t>16930; 34053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41108; 67983</t>
+          <t>44966; 71205</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>36663</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14487; 30905</t>
+          <t>15510; 32649</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8094; 19796</t>
+          <t>8869; 21312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26067; 46895</t>
+          <t>26949; 48030</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>30084</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5206; 31651</t>
+          <t>11659; 27857</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6961; 17286</t>
+          <t>7543; 17359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10173; 44606</t>
+          <t>22155; 41990</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57735</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87311</t>
+          <t>97248</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42992; 72491</t>
+          <t>47626; 79142</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14609; 41864</t>
+          <t>25371; 42957</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61834; 108565</t>
+          <t>79644; 118552</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>49167</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5120; 18086</t>
+          <t>8189; 23510</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22678; 44503</t>
+          <t>26963; 45317</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31934; 54754</t>
+          <t>39847; 62905</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>26071</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2486</t>
+          <t>0; 2590</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17012; 34166</t>
+          <t>17955; 34928</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18150; 35160</t>
+          <t>18060; 37011</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>137150</t>
+          <t>151523</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>133495</t>
+          <t>144564</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>270645</t>
+          <t>296087</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>107076; 164267</t>
+          <t>131892; 178506</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105594; 154244</t>
+          <t>129687; 166928</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230725; 307701</t>
+          <t>269459; 330897</t>
         </is>
       </c>
     </row>
